--- a/artfynd/A 25977-2025 artfynd.xlsx
+++ b/artfynd/A 25977-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>207146</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596236.0874087391</v>
+        <v>596236</v>
       </c>
       <c r="R2" t="n">
-        <v>7192557.182879014</v>
+        <v>7192557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
